--- a/Professional/3-PhD/Application_List.xlsx
+++ b/Professional/3-PhD/Application_List.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29328"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29426"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\scott\Documents\Folder\Professional\3-PhD\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2246AEC1-2D3F-4A61-B208-B1DFA71C6DEB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A07B2CBF-976E-4134-9E5F-C87DE49CC448}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="23260" windowHeight="14860" xr2:uid="{21F9BD98-567A-478A-BE72-D5B7482DEFC2}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="25" uniqueCount="24">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="26" uniqueCount="25">
   <si>
     <t>School</t>
   </si>
@@ -108,6 +108,9 @@
   </si>
   <si>
     <t>UCSD</t>
+  </si>
+  <si>
+    <t>snguyen7299@sdusu.edu</t>
   </si>
 </sst>
 </file>
@@ -491,7 +494,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D1B43451-2806-41C1-8D5A-A6AE57900CAF}">
-  <dimension ref="A1:F6"/>
+  <dimension ref="A1:G6"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="31.08984375" bestFit="1" customWidth="1"/>
@@ -499,9 +502,10 @@
     <col min="3" max="3" width="15" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="10.54296875" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="22.7265625" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="21.7265625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -521,7 +525,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="2" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A2" s="1" t="s">
         <v>6</v>
       </c>
@@ -541,7 +545,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="3" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A3" s="1" t="s">
         <v>22</v>
       </c>
@@ -560,8 +564,11 @@
       <c r="F3" s="1" t="s">
         <v>21</v>
       </c>
+      <c r="G3" s="1" t="s">
+        <v>24</v>
+      </c>
     </row>
-    <row r="4" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A4" s="1" t="s">
         <v>23</v>
       </c>
@@ -569,7 +576,7 @@
       <c r="D4" s="2"/>
       <c r="F4" s="1"/>
     </row>
-    <row r="5" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A5" s="1" t="s">
         <v>9</v>
       </c>
@@ -589,7 +596,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="6" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A6" t="s">
         <v>18</v>
       </c>
@@ -613,6 +620,7 @@
     <hyperlink ref="A4" r:id="rId8" xr:uid="{8EDAD41E-8481-41F4-98B1-0D8FED07F7EA}"/>
     <hyperlink ref="A2" r:id="rId9" xr:uid="{6A7CE213-7953-4620-95A7-8C0E55153C0F}"/>
     <hyperlink ref="A5" r:id="rId10" xr:uid="{62528FF8-2DF2-4CD4-BDA6-CD47367B1F21}"/>
+    <hyperlink ref="G3" r:id="rId11" xr:uid="{BA29FF2A-F6A0-45C6-9DF4-FA3C3EACBFBB}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/Professional/3-PhD/Application_List.xlsx
+++ b/Professional/3-PhD/Application_List.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29426"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29530"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\scott\Documents\Folder\Professional\3-PhD\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A07B2CBF-976E-4134-9E5F-C87DE49CC448}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8406A31C-77AE-42EF-BBF3-1E0C63D282C0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="23260" windowHeight="14860" xr2:uid="{21F9BD98-567A-478A-BE72-D5B7482DEFC2}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="26" uniqueCount="25">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="21" uniqueCount="20">
   <si>
     <t>School</t>
   </si>
@@ -65,25 +65,10 @@
     <t>No</t>
   </si>
   <si>
-    <t>The University of Arizona</t>
-  </si>
-  <si>
-    <t>Dr. Jekan Thanga</t>
-  </si>
-  <si>
-    <t>Yes</t>
-  </si>
-  <si>
     <t>Email</t>
   </si>
   <si>
-    <t>jekan@arizona.edu</t>
-  </si>
-  <si>
     <t>damicos@stanford.edu</t>
-  </si>
-  <si>
-    <t>SpaceTREx</t>
   </si>
   <si>
     <t>Personal Website</t>
@@ -494,7 +479,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D1B43451-2806-41C1-8D5A-A6AE57900CAF}">
-  <dimension ref="A1:G6"/>
+  <dimension ref="A1:G5"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="31.08984375" bestFit="1" customWidth="1"/>
@@ -522,7 +507,7 @@
         <v>7</v>
       </c>
       <c r="F1" t="s">
-        <v>12</v>
+        <v>9</v>
       </c>
     </row>
     <row r="2" spans="1:7" x14ac:dyDescent="0.35">
@@ -542,18 +527,18 @@
         <v>8</v>
       </c>
       <c r="F2" s="1" t="s">
-        <v>14</v>
+        <v>10</v>
       </c>
     </row>
     <row r="3" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A3" s="1" t="s">
-        <v>22</v>
+        <v>17</v>
       </c>
       <c r="B3" t="s">
-        <v>19</v>
+        <v>14</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="D3" s="2">
         <v>45992</v>
@@ -562,65 +547,42 @@
         <v>8</v>
       </c>
       <c r="F3" s="1" t="s">
-        <v>21</v>
+        <v>16</v>
       </c>
       <c r="G3" s="1" t="s">
-        <v>24</v>
+        <v>19</v>
       </c>
     </row>
     <row r="4" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A4" s="1" t="s">
-        <v>23</v>
+        <v>18</v>
       </c>
       <c r="C4" s="1"/>
       <c r="D4" s="2"/>
       <c r="F4" s="1"/>
     </row>
     <row r="5" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A5" s="1" t="s">
-        <v>9</v>
+      <c r="A5" t="s">
+        <v>13</v>
       </c>
       <c r="B5" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="D5" s="2">
-        <v>45658</v>
-      </c>
-      <c r="E5" t="s">
         <v>11</v>
       </c>
-      <c r="F5" s="1" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="6" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A6" t="s">
-        <v>18</v>
-      </c>
-      <c r="B6" t="s">
-        <v>17</v>
-      </c>
-      <c r="C6" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="D6" s="2"/>
+      <c r="D5" s="2"/>
     </row>
   </sheetData>
   <hyperlinks>
     <hyperlink ref="C2" r:id="rId1" xr:uid="{9CA7BBFC-305D-4AD4-ABCA-7DD54B962936}"/>
     <hyperlink ref="F2" r:id="rId2" xr:uid="{38CE503E-AA4E-4B47-9D82-DBE782C600EE}"/>
-    <hyperlink ref="C6" r:id="rId3" xr:uid="{5F4431D8-366C-4931-9D9A-5C9D7F6ADDDE}"/>
+    <hyperlink ref="C5" r:id="rId3" xr:uid="{5F4431D8-366C-4931-9D9A-5C9D7F6ADDDE}"/>
     <hyperlink ref="F3" r:id="rId4" xr:uid="{AF9F6376-5CA9-41AA-ADA8-0BC865FB972F}"/>
     <hyperlink ref="A3" r:id="rId5" xr:uid="{B15B4761-07EF-4D5C-8433-D2E588AFC49B}"/>
-    <hyperlink ref="F5" r:id="rId6" xr:uid="{C4C527D4-7FD3-447C-B48D-BF8039A533CC}"/>
-    <hyperlink ref="C5" r:id="rId7" xr:uid="{6672E727-975C-4BD1-B2DA-6CA77FFF45CA}"/>
-    <hyperlink ref="A4" r:id="rId8" xr:uid="{8EDAD41E-8481-41F4-98B1-0D8FED07F7EA}"/>
-    <hyperlink ref="A2" r:id="rId9" xr:uid="{6A7CE213-7953-4620-95A7-8C0E55153C0F}"/>
-    <hyperlink ref="A5" r:id="rId10" xr:uid="{62528FF8-2DF2-4CD4-BDA6-CD47367B1F21}"/>
-    <hyperlink ref="G3" r:id="rId11" xr:uid="{BA29FF2A-F6A0-45C6-9DF4-FA3C3EACBFBB}"/>
+    <hyperlink ref="A4" r:id="rId6" xr:uid="{8EDAD41E-8481-41F4-98B1-0D8FED07F7EA}"/>
+    <hyperlink ref="A2" r:id="rId7" xr:uid="{6A7CE213-7953-4620-95A7-8C0E55153C0F}"/>
+    <hyperlink ref="G3" r:id="rId8" xr:uid="{BA29FF2A-F6A0-45C6-9DF4-FA3C3EACBFBB}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
